--- a/別紙/別紙E3_PJアカウント.xlsx
+++ b/別紙/別紙E3_PJアカウント.xlsx
@@ -28,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="MeiryoUI"/>
       <charset val="128"/>
@@ -130,13 +130,23 @@
       <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <strike val="1"/>
+      <color rgb="00808080"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE4E1"/>
+        <bgColor rgb="00FFE4E1"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -193,7 +203,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -287,6 +297,51 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -686,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A2:M47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5703125" defaultRowHeight="15"/>
   <cols>
     <col width="3.5703125" customWidth="1" style="1" min="1" max="1"/>
@@ -715,7 +770,6 @@
     <col width="7.5703125" customWidth="1" style="1" min="32" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="16" customHeight="1" s="18">
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
@@ -862,35 +916,35 @@
       </c>
     </row>
     <row r="7" ht="76" customHeight="1" s="18">
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>wii@codium.co</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>CODIUM</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>CODIUM 【退職 2026-09-29】</t>
+        </is>
+      </c>
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Wai Yan Aung</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="37" t="inlineStr">
         <is>
           <t>IAM user</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="38" t="inlineStr">
         <is>
           <t>AmazonEC2FullAccess
 AmazonECS_FullAccess 
@@ -898,25 +952,25 @@
 CODIM_wifi_onry</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="38" t="inlineStr">
         <is>
           <t>スマホ認証</t>
         </is>
       </c>
-      <c r="J7" s="23" t="n">
+      <c r="J7" s="39" t="n">
         <v>45705</v>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="39" t="inlineStr">
         <is>
           <t>半年に一度</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="L7" s="37" t="inlineStr">
         <is>
           <t>エスブランド</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="40" t="inlineStr">
         <is>
           <t>ETR</t>
         </is>
@@ -1110,52 +1164,52 @@
     </row>
     <row r="12" ht="38" customHeight="1" s="18">
       <c r="A12" s="14" t="n"/>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>ETRCARS　web</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="D12" s="41" t="inlineStr">
         <is>
           <t>codium</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>CODIUM</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>CODIUM 【退職 2026-09-29】</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Wai Yan Aung</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>administrator</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="37" t="inlineStr">
         <is>
           <t>実績データ、車両データ閲覧</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="37" t="inlineStr">
         <is>
           <t>パスワード</t>
         </is>
       </c>
-      <c r="J12" s="23" t="n"/>
-      <c r="K12" s="23" t="n"/>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="J12" s="39" t="n"/>
+      <c r="K12" s="39" t="n"/>
+      <c r="L12" s="37" t="inlineStr">
         <is>
           <t>エスブランド</t>
         </is>
       </c>
-      <c r="M12" s="25" t="inlineStr">
+      <c r="M12" s="40" t="inlineStr">
         <is>
           <t>ETR</t>
         </is>
@@ -1230,58 +1284,58 @@
       <c r="M14" s="14" t="n"/>
     </row>
     <row r="15" ht="38" customHeight="1" s="18">
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>@waiyan.a</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>CODIUM</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>CODIUM 【退職 2026-09-29】</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Wai Yan Aung</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="37" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="37" t="inlineStr">
         <is>
           <t>Source Control and CI/CD</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I15" s="37" t="inlineStr">
         <is>
           <t>パスワード</t>
         </is>
       </c>
-      <c r="J15" s="23" t="n">
+      <c r="J15" s="39" t="n">
         <v>44958</v>
       </c>
-      <c r="K15" s="23" t="inlineStr">
+      <c r="K15" s="39" t="inlineStr">
         <is>
           <t>半年に一度</t>
         </is>
       </c>
-      <c r="L15" s="21" t="inlineStr">
+      <c r="L15" s="37" t="inlineStr">
         <is>
           <t>エスブランド</t>
         </is>
       </c>
-      <c r="M15" s="25" t="inlineStr">
+      <c r="M15" s="40" t="inlineStr">
         <is>
           <t>ETR</t>
         </is>
@@ -1752,7 +1806,6 @@
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43" ht="16" customHeight="1" s="18">
       <c r="C43" s="3" t="n"/>
     </row>
@@ -2089,123 +2142,125 @@
       </c>
     </row>
     <row r="4" ht="37" customHeight="1" s="18">
-      <c r="A4" s="21" t="n">
+      <c r="A4" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>wii@codium.co</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>CODIUM</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>Wai Yan Aung</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
+        <is>
+          <t>Wai Yan Aung 【退職 2026-09-29】</t>
+        </is>
+      </c>
+      <c r="F4" s="43" t="inlineStr">
         <is>
           <t>IAM user</t>
         </is>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="44" t="n">
         <v>45930</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="45" t="n">
         <v>45896</v>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="46" t="inlineStr">
         <is>
           <t>有効</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="46" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="46" t="inlineStr">
         <is>
           <t>佐野</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="46" t="inlineStr">
         <is>
           <t>山田</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="46" t="inlineStr">
         <is>
           <t>MFAを設定してください</t>
         </is>
       </c>
-      <c r="O4" s="30" t="n">
+      <c r="N4" s="47" t="n"/>
+      <c r="O4" s="44" t="n">
         <v>46001</v>
       </c>
-      <c r="P4" s="12" t="n">
+      <c r="P4" s="45" t="n">
         <v>46001</v>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="46" t="inlineStr">
         <is>
           <t>有効</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr">
+      <c r="R4" s="46" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="S4" s="46" t="inlineStr">
         <is>
           <t>佐野</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="46" t="inlineStr">
         <is>
           <t>山田</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr">
+      <c r="U4" s="46" t="inlineStr">
         <is>
           <t>無し</t>
         </is>
       </c>
-      <c r="W4" s="30" t="n">
+      <c r="V4" s="47" t="n"/>
+      <c r="W4" s="44" t="n">
         <v>46027</v>
       </c>
-      <c r="X4" s="12" t="n">
+      <c r="X4" s="45" t="n">
         <v>46026</v>
       </c>
-      <c r="Y4" s="11" t="inlineStr">
+      <c r="Y4" s="46" t="inlineStr">
         <is>
           <t>有効</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
+      <c r="Z4" s="46" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="AA4" s="11" t="inlineStr">
+      <c r="AA4" s="46" t="inlineStr">
         <is>
           <t>佐野</t>
         </is>
       </c>
-      <c r="AB4" s="11" t="inlineStr">
+      <c r="AB4" s="46" t="inlineStr">
         <is>
           <t>山田</t>
         </is>
       </c>
-      <c r="AC4" s="11" t="inlineStr">
+      <c r="AC4" s="46" t="inlineStr">
         <is>
           <t>無し</t>
         </is>
@@ -2503,85 +2558,87 @@
       </c>
     </row>
     <row r="9" ht="37" customHeight="1" s="18">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>ETRCARS　web</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="48" t="inlineStr">
         <is>
           <t>codium</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="43" t="inlineStr">
         <is>
           <t>CODIUM</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>Wai Yan Aung</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>Wai Yan Aung 【退職 2026-09-29】</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="inlineStr">
         <is>
           <t>administrator</t>
         </is>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="44" t="n">
         <v>45930</v>
       </c>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="H9" s="46" t="n"/>
+      <c r="I9" s="46" t="inlineStr">
         <is>
           <t>有効</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="46" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="O9" s="30" t="n"/>
-      <c r="P9" s="11" t="n"/>
-      <c r="Q9" s="11" t="n"/>
-      <c r="R9" s="11" t="n"/>
-      <c r="S9" s="11" t="n"/>
-      <c r="T9" s="11" t="n"/>
-      <c r="U9" s="11" t="n"/>
-      <c r="W9" s="30" t="n">
+      <c r="K9" s="46" t="n"/>
+      <c r="L9" s="46" t="n"/>
+      <c r="M9" s="46" t="n"/>
+      <c r="N9" s="47" t="n"/>
+      <c r="O9" s="44" t="n"/>
+      <c r="P9" s="46" t="n"/>
+      <c r="Q9" s="46" t="n"/>
+      <c r="R9" s="46" t="n"/>
+      <c r="S9" s="46" t="n"/>
+      <c r="T9" s="46" t="n"/>
+      <c r="U9" s="46" t="n"/>
+      <c r="V9" s="47" t="n"/>
+      <c r="W9" s="44" t="n">
         <v>46027</v>
       </c>
-      <c r="X9" s="12" t="n">
+      <c r="X9" s="45" t="n">
         <v>46026</v>
       </c>
-      <c r="Y9" s="11" t="inlineStr">
+      <c r="Y9" s="46" t="inlineStr">
         <is>
           <t>有効</t>
         </is>
       </c>
-      <c r="Z9" s="11" t="inlineStr">
+      <c r="Z9" s="46" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="AA9" s="11" t="inlineStr">
+      <c r="AA9" s="46" t="inlineStr">
         <is>
           <t>佐野</t>
         </is>
       </c>
-      <c r="AB9" s="11" t="inlineStr">
+      <c r="AB9" s="46" t="inlineStr">
         <is>
           <t>山田</t>
         </is>
       </c>
-      <c r="AC9" s="11" t="inlineStr">
+      <c r="AC9" s="46" t="inlineStr">
         <is>
           <t>無し</t>
         </is>
@@ -2676,83 +2733,85 @@
       <c r="A11" s="14" t="n"/>
     </row>
     <row r="12" ht="37" customHeight="1" s="18">
-      <c r="A12" s="21" t="n">
+      <c r="A12" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>@waiyan.a</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t>CODIUM</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Wai Yan Aung</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>Wai Yan Aung 【退職 2026-09-29】</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="44" t="n">
         <v>45930</v>
       </c>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="H12" s="46" t="n"/>
+      <c r="I12" s="46" t="inlineStr">
         <is>
           <t>有効</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="46" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="11" t="n"/>
-      <c r="O12" s="30" t="n">
+      <c r="K12" s="46" t="n"/>
+      <c r="L12" s="46" t="n"/>
+      <c r="M12" s="46" t="n"/>
+      <c r="N12" s="47" t="n"/>
+      <c r="O12" s="44" t="n">
         <v>46001</v>
       </c>
-      <c r="P12" s="11" t="n"/>
-      <c r="Q12" s="11" t="inlineStr">
+      <c r="P12" s="46" t="n"/>
+      <c r="Q12" s="46" t="inlineStr">
         <is>
           <t>有効</t>
         </is>
       </c>
-      <c r="R12" s="11" t="inlineStr">
+      <c r="R12" s="46" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="S12" s="11" t="inlineStr">
+      <c r="S12" s="46" t="inlineStr">
         <is>
           <t>佐野</t>
         </is>
       </c>
-      <c r="T12" s="11" t="n"/>
-      <c r="U12" s="11" t="inlineStr">
+      <c r="T12" s="46" t="n"/>
+      <c r="U12" s="46" t="inlineStr">
         <is>
           <t>現地監査</t>
         </is>
       </c>
-      <c r="W12" s="31" t="n"/>
-      <c r="X12" s="11" t="n"/>
-      <c r="Y12" s="11" t="n"/>
-      <c r="Z12" s="11" t="n"/>
-      <c r="AA12" s="11" t="n"/>
-      <c r="AB12" s="11" t="n"/>
-      <c r="AC12" s="11" t="n"/>
+      <c r="V12" s="47" t="n"/>
+      <c r="W12" s="46" t="n"/>
+      <c r="X12" s="46" t="n"/>
+      <c r="Y12" s="46" t="n"/>
+      <c r="Z12" s="46" t="n"/>
+      <c r="AA12" s="46" t="n"/>
+      <c r="AB12" s="46" t="n"/>
+      <c r="AC12" s="46" t="n"/>
     </row>
     <row r="13" ht="37" customHeight="1" s="18">
       <c r="A13" s="21" t="n">
@@ -3237,7 +3296,6 @@
       <c r="AB19" s="11" t="n"/>
       <c r="AC19" s="11" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="G21" s="0" t="inlineStr">
         <is>
@@ -3392,48 +3450,57 @@
       <c r="U23" s="11" t="n"/>
     </row>
     <row r="24" ht="37" customHeight="1" s="18">
-      <c r="A24" s="21" t="n">
+      <c r="A24" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>wii@codium.co</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="37" t="inlineStr">
         <is>
           <t>CODIUM</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>Wai Yan Aung</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="E24" s="37" t="inlineStr">
+        <is>
+          <t>Wai Yan Aung 【退職 2026-09-29】</t>
+        </is>
+      </c>
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>IAM user</t>
         </is>
       </c>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="11" t="n"/>
-      <c r="J24" s="11" t="n"/>
-      <c r="K24" s="11" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="11" t="n"/>
-      <c r="O24" s="13" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="11" t="n"/>
-      <c r="R24" s="11" t="n"/>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="11" t="n"/>
-      <c r="U24" s="11" t="n"/>
+      <c r="G24" s="50" t="n"/>
+      <c r="H24" s="51" t="n"/>
+      <c r="I24" s="52" t="n"/>
+      <c r="J24" s="52" t="n"/>
+      <c r="K24" s="52" t="n"/>
+      <c r="L24" s="52" t="n"/>
+      <c r="M24" s="52" t="n"/>
+      <c r="N24" s="53" t="n"/>
+      <c r="O24" s="50" t="n"/>
+      <c r="P24" s="51" t="n"/>
+      <c r="Q24" s="52" t="n"/>
+      <c r="R24" s="52" t="n"/>
+      <c r="S24" s="52" t="n"/>
+      <c r="T24" s="52" t="n"/>
+      <c r="U24" s="52" t="n"/>
+      <c r="V24" s="53" t="n"/>
+      <c r="W24" s="53" t="n"/>
+      <c r="X24" s="53" t="n"/>
+      <c r="Y24" s="53" t="n"/>
+      <c r="Z24" s="53" t="n"/>
+      <c r="AA24" s="53" t="n"/>
+      <c r="AB24" s="53" t="n"/>
+      <c r="AC24" s="53" t="n"/>
     </row>
     <row r="25" ht="37" customHeight="1" s="18">
       <c r="A25" s="21" t="n">
@@ -3569,48 +3636,57 @@
       <c r="U28" s="11" t="n"/>
     </row>
     <row r="29" ht="37" customHeight="1" s="18">
-      <c r="A29" s="21" t="n">
+      <c r="A29" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>ETRCARS　web</t>
         </is>
       </c>
-      <c r="C29" s="32" t="inlineStr">
+      <c r="C29" s="41" t="inlineStr">
         <is>
           <t>codium</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="37" t="inlineStr">
         <is>
           <t>CODIUM</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>Wai Yan Aung</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
+        <is>
+          <t>Wai Yan Aung 【退職 2026-09-29】</t>
+        </is>
+      </c>
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>administrator</t>
         </is>
       </c>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="O29" s="13" t="n"/>
-      <c r="P29" s="11" t="n"/>
-      <c r="Q29" s="11" t="n"/>
-      <c r="R29" s="11" t="n"/>
-      <c r="S29" s="11" t="n"/>
-      <c r="T29" s="11" t="n"/>
-      <c r="U29" s="11" t="n"/>
+      <c r="G29" s="50" t="n"/>
+      <c r="H29" s="52" t="n"/>
+      <c r="I29" s="52" t="n"/>
+      <c r="J29" s="52" t="n"/>
+      <c r="K29" s="52" t="n"/>
+      <c r="L29" s="52" t="n"/>
+      <c r="M29" s="52" t="n"/>
+      <c r="N29" s="53" t="n"/>
+      <c r="O29" s="50" t="n"/>
+      <c r="P29" s="52" t="n"/>
+      <c r="Q29" s="52" t="n"/>
+      <c r="R29" s="52" t="n"/>
+      <c r="S29" s="52" t="n"/>
+      <c r="T29" s="52" t="n"/>
+      <c r="U29" s="52" t="n"/>
+      <c r="V29" s="53" t="n"/>
+      <c r="W29" s="53" t="n"/>
+      <c r="X29" s="53" t="n"/>
+      <c r="Y29" s="53" t="n"/>
+      <c r="Z29" s="53" t="n"/>
+      <c r="AA29" s="53" t="n"/>
+      <c r="AB29" s="53" t="n"/>
+      <c r="AC29" s="53" t="n"/>
     </row>
     <row r="30" ht="37" customHeight="1" s="18">
       <c r="A30" s="21" t="n">
@@ -3656,50 +3732,58 @@
       <c r="T30" s="11" t="n"/>
       <c r="U30" s="11" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="37" customHeight="1" s="18">
-      <c r="A32" s="21" t="n">
+      <c r="A32" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="37" t="inlineStr">
         <is>
           <t>GitLab</t>
         </is>
       </c>
-      <c r="C32" s="35" t="inlineStr">
+      <c r="C32" s="42" t="inlineStr">
         <is>
           <t>@waiyan.a</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="37" t="inlineStr">
         <is>
           <t>CODIUM</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>Wai Yan Aung</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="E32" s="37" t="inlineStr">
+        <is>
+          <t>Wai Yan Aung 【退職 2026-09-29】</t>
+        </is>
+      </c>
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="11" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-      <c r="O32" s="13" t="n"/>
-      <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="11" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="11" t="n"/>
-      <c r="U32" s="11" t="n"/>
+      <c r="G32" s="50" t="n"/>
+      <c r="H32" s="52" t="n"/>
+      <c r="I32" s="52" t="n"/>
+      <c r="J32" s="52" t="n"/>
+      <c r="K32" s="52" t="n"/>
+      <c r="L32" s="52" t="n"/>
+      <c r="M32" s="52" t="n"/>
+      <c r="N32" s="53" t="n"/>
+      <c r="O32" s="50" t="n"/>
+      <c r="P32" s="52" t="n"/>
+      <c r="Q32" s="52" t="n"/>
+      <c r="R32" s="52" t="n"/>
+      <c r="S32" s="52" t="n"/>
+      <c r="T32" s="52" t="n"/>
+      <c r="U32" s="52" t="n"/>
+      <c r="V32" s="53" t="n"/>
+      <c r="W32" s="53" t="n"/>
+      <c r="X32" s="53" t="n"/>
+      <c r="Y32" s="53" t="n"/>
+      <c r="Z32" s="53" t="n"/>
+      <c r="AA32" s="53" t="n"/>
+      <c r="AB32" s="53" t="n"/>
+      <c r="AC32" s="53" t="n"/>
     </row>
     <row r="33" ht="37" customHeight="1" s="18">
       <c r="A33" s="21" t="n">
